--- a/tabelas/descritiva_15rs_2026.xlsx
+++ b/tabelas/descritiva_15rs_2026.xlsx
@@ -122,12 +122,12 @@
     <t>Florida</t>
   </si>
   <si>
+    <t>Iguaracu</t>
+  </si>
+  <si>
     <t>Mandaguari</t>
   </si>
   <si>
-    <t>Iguaracu</t>
-  </si>
-  <si>
     <t>Doutor Camargo</t>
   </si>
   <si>
@@ -140,6 +140,9 @@
     <t>n_total</t>
   </si>
   <si>
+    <t>Bairro</t>
+  </si>
+  <si>
     <t>Obesidade</t>
   </si>
   <si>
@@ -153,9 +156,6 @@
   </si>
   <si>
     <t>Evolução (Desfecho)</t>
-  </si>
-  <si>
-    <t>Bairro</t>
   </si>
   <si>
     <t>Critério Confirmação</t>
@@ -661,25 +661,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>364.7</v>
+        <v>361.1</v>
       </c>
       <c r="F2">
-        <v>36.8</v>
+        <v>14.7</v>
       </c>
       <c r="G2">
-        <v>10.1</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -869,22 +869,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>863</v>
+        <v>837</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D10">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E10">
-        <v>200.9</v>
+        <v>194.8</v>
       </c>
       <c r="F10">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="G10">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H10">
         <v>28.3</v>
@@ -921,7 +921,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <v>180.2</v>
+        <v>175.9</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -956,7 +956,7 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>160.6</v>
+        <v>144.5</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -973,16 +973,16 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>145.7</v>
+        <v>124.9</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -999,25 +999,25 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>129.6</v>
+        <v>122.9</v>
       </c>
       <c r="F15">
         <v>4.5</v>
       </c>
       <c r="G15">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H15">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1051,25 +1051,25 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E17">
-        <v>89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F17">
+        <v>5.5</v>
+      </c>
+      <c r="G17">
         <v>6.2</v>
       </c>
-      <c r="G17">
-        <v>7</v>
-      </c>
       <c r="H17">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1219,10 +1219,10 @@
         <v>46.5</v>
       </c>
       <c r="F23">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1311,16 +1311,16 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>36.5</v>
+        <v>35.1</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>78.59999999999999</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1337,16 +1337,16 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>35.1</v>
+        <v>33.9</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>50</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1410,10 +1410,10 @@
         <v>39</v>
       </c>
       <c r="B2">
-        <v>60.2</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1421,10 +1421,10 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>60.6</v>
+        <v>59.8</v>
       </c>
       <c r="C3">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1432,10 +1432,10 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>60.8</v>
+        <v>60.3</v>
       </c>
       <c r="C4">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1443,10 +1443,10 @@
         <v>42</v>
       </c>
       <c r="B5">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="C5">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1454,10 +1454,10 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>87.2</v>
+        <v>60.5</v>
       </c>
       <c r="C6">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1465,10 +1465,10 @@
         <v>44</v>
       </c>
       <c r="B7">
-        <v>90.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="C7">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1476,10 +1476,10 @@
         <v>45</v>
       </c>
       <c r="B8">
-        <v>94.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="C8">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1487,10 +1487,10 @@
         <v>46</v>
       </c>
       <c r="B9">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="C9">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1501,7 +1501,7 @@
         <v>98.5</v>
       </c>
       <c r="C10">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1512,7 +1512,7 @@
         <v>98.90000000000001</v>
       </c>
       <c r="C11">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1520,10 +1520,10 @@
         <v>49</v>
       </c>
       <c r="B12">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="C12">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1534,7 +1534,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1545,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1556,7 +1556,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1567,7 +1567,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>1361</v>
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -1593,24 +1593,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C2">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C3">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1618,10 +1618,10 @@
         <v>57</v>
       </c>
       <c r="B4">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C4">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1629,7 +1629,7 @@
         <v>58</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>11.8</v>
@@ -1640,7 +1640,7 @@
         <v>59</v>
       </c>
       <c r="B6">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C6">
         <v>10.9</v>
@@ -1651,7 +1651,7 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1659,18 +1659,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>34</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>27</v>
@@ -1684,7 +1684,7 @@
         <v>61</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>0.8</v>
@@ -1698,7 +1698,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -1733,10 +1733,10 @@
         <v>128</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1744,7 +1744,7 @@
         <v>66</v>
       </c>
       <c r="B3">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>67</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1800,13 +1800,13 @@
         <v>70</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1814,7 +1814,7 @@
         <v>71</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         <v>72</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1842,13 +1842,13 @@
         <v>73</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1856,7 +1856,7 @@
         <v>74</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1870,13 +1870,13 @@
         <v>75</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="C12">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D12">
-        <v>15.8</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -1922,13 +1922,13 @@
         <v>66</v>
       </c>
       <c r="B3">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C3">
         <v>45</v>
       </c>
       <c r="D3">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1936,13 +1936,13 @@
         <v>67</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1978,13 +1978,13 @@
         <v>70</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>34.3</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1992,13 +1992,13 @@
         <v>71</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>15</v>
       </c>
       <c r="D8">
-        <v>34.1</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2006,13 +2006,13 @@
         <v>72</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9">
-        <v>25.6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2020,13 +2020,13 @@
         <v>73</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>33.8</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2034,13 +2034,13 @@
         <v>74</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11">
         <v>28</v>
       </c>
       <c r="D11">
-        <v>24.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2048,13 +2048,13 @@
         <v>75</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="C12">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D12">
-        <v>28.4</v>
+        <v>27.4</v>
       </c>
     </row>
   </sheetData>
@@ -2083,10 +2083,10 @@
         <v>78</v>
       </c>
       <c r="B2">
-        <v>788</v>
+        <v>739</v>
       </c>
       <c r="C2">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2094,10 +2094,10 @@
         <v>79</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2137,10 +2137,10 @@
         <v>82</v>
       </c>
       <c r="B2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2148,10 +2148,10 @@
         <v>83</v>
       </c>
       <c r="B3">
-        <v>984</v>
+        <v>959</v>
       </c>
       <c r="C3">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2159,10 +2159,10 @@
         <v>84</v>
       </c>
       <c r="B4">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C4">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
     </row>
   </sheetData>
@@ -2194,7 +2194,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2202,10 +2202,10 @@
         <v>86</v>
       </c>
       <c r="B3">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2213,10 +2213,10 @@
         <v>87</v>
       </c>
       <c r="B4">
-        <v>815</v>
+        <v>787</v>
       </c>
       <c r="C4">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/descritiva_15rs_2026.xlsx
+++ b/tabelas/descritiva_15rs_2026.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
   <si>
     <t>municipio</t>
   </si>
@@ -50,13 +50,16 @@
     <t>Nova Esperanca</t>
   </si>
   <si>
+    <t>Santa Ines</t>
+  </si>
+  <si>
     <t>Uniflor</t>
   </si>
   <si>
     <t>Ourizona</t>
   </si>
   <si>
-    <t>Santa Ines</t>
+    <t>Sao Jorge Do Ivai</t>
   </si>
   <si>
     <t>Atalaia</t>
@@ -68,9 +71,6 @@
     <t>Nossa Senhora Das Gracas</t>
   </si>
   <si>
-    <t>Sao Jorge Do Ivai</t>
-  </si>
-  <si>
     <t>Maringa</t>
   </si>
   <si>
@@ -80,12 +80,12 @@
     <t>Colorado</t>
   </si>
   <si>
+    <t>Florai</t>
+  </si>
+  <si>
     <t>Itambe</t>
   </si>
   <si>
-    <t>Florai</t>
-  </si>
-  <si>
     <t>Marialva</t>
   </si>
   <si>
@@ -95,30 +95,30 @@
     <t>Sarandi</t>
   </si>
   <si>
+    <t>Munhoz De Melo</t>
+  </si>
+  <si>
+    <t>Lobato</t>
+  </si>
+  <si>
     <t>Astorga</t>
   </si>
   <si>
     <t>Floresta</t>
   </si>
   <si>
-    <t>Munhoz De Melo</t>
+    <t>Paicandu</t>
   </si>
   <si>
     <t>Mandaguacu</t>
   </si>
   <si>
-    <t>Paicandu</t>
-  </si>
-  <si>
     <t>Presidente Castelo Branco</t>
   </si>
   <si>
     <t>Santa Fe</t>
   </si>
   <si>
-    <t>Lobato</t>
-  </si>
-  <si>
     <t>Florida</t>
   </si>
   <si>
@@ -143,30 +143,27 @@
     <t>Obesidade</t>
   </si>
   <si>
+    <t>Cardiopatia</t>
+  </si>
+  <si>
     <t>Diabetes</t>
   </si>
   <si>
-    <t>Cardiopatia</t>
-  </si>
-  <si>
     <t>Imunodepressão</t>
   </si>
   <si>
     <t>Evolução (Desfecho)</t>
   </si>
   <si>
-    <t>Bairro</t>
-  </si>
-  <si>
     <t>Critério Confirmação</t>
   </si>
   <si>
+    <t>Raça/Cor</t>
+  </si>
+  <si>
     <t>Antiviral</t>
   </si>
   <si>
-    <t>Raça/Cor</t>
-  </si>
-  <si>
     <t>Data Internação</t>
   </si>
   <si>
@@ -206,10 +203,10 @@
     <t>Doença Renal</t>
   </si>
   <si>
+    <t>Síndrome de Down</t>
+  </si>
+  <si>
     <t>Doença Hepática</t>
-  </si>
-  <si>
-    <t>Síndrome de Down</t>
   </si>
   <si>
     <t>faixa_etaria</t>
@@ -661,25 +658,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>364.7</v>
+        <v>372.1</v>
       </c>
       <c r="F2">
-        <v>36.8</v>
+        <v>33.2</v>
       </c>
       <c r="G2">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -687,22 +684,22 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>284.9</v>
+        <v>286.5</v>
       </c>
       <c r="F3">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -713,25 +710,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>250.5</v>
+        <v>284.9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H4">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -739,16 +736,16 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>229.2</v>
+        <v>250.5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -757,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -765,16 +762,16 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>222.4</v>
+        <v>232.1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -783,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -791,25 +788,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>220.8</v>
+        <v>222.4</v>
       </c>
       <c r="F7">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -817,25 +814,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>218</v>
+        <v>220.8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>37.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -843,25 +840,25 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9">
-        <v>212.8</v>
+        <v>218</v>
       </c>
       <c r="F9">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>27.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -869,25 +866,25 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>863</v>
+        <v>907</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D10">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E10">
-        <v>200.9</v>
+        <v>211.1</v>
       </c>
       <c r="F10">
-        <v>20.2</v>
+        <v>16.8</v>
       </c>
       <c r="G10">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="H10">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -947,7 +944,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -956,7 +953,7 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>160.6</v>
+        <v>145.7</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -965,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -973,7 +970,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -982,7 +979,7 @@
         <v>2</v>
       </c>
       <c r="E14">
-        <v>145.7</v>
+        <v>144.5</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -991,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>28.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -999,25 +996,25 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15">
-        <v>129.6</v>
+        <v>138.6</v>
       </c>
       <c r="F15">
         <v>4.5</v>
       </c>
       <c r="G15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H15">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1051,25 +1048,25 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E17">
-        <v>89</v>
+        <v>95.2</v>
       </c>
       <c r="F17">
         <v>6.2</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H17">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1077,25 +1074,25 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
       <c r="E18">
-        <v>53.4</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F18">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1103,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1112,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>52.1</v>
+        <v>63.7</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1121,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1129,16 +1126,16 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>49.3</v>
+        <v>57.2</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1147,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1155,16 +1152,16 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>49.2</v>
+        <v>52.1</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1173,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>41.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1181,25 +1178,25 @@
         <v>28</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>47.2</v>
+        <v>49.3</v>
       </c>
       <c r="F22">
         <v>2.1</v>
       </c>
       <c r="G22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H22">
-        <v>60.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1207,25 +1204,25 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>46.5</v>
+        <v>49.2</v>
       </c>
       <c r="F23">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1233,25 +1230,25 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>42.6</v>
+        <v>46.5</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1259,16 +1256,16 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1277,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1391,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1410,10 +1407,10 @@
         <v>39</v>
       </c>
       <c r="B2">
-        <v>60.2</v>
+        <v>61.2</v>
       </c>
       <c r="C2">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1421,10 +1418,10 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>60.6</v>
+        <v>61.7</v>
       </c>
       <c r="C3">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1432,10 +1429,10 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="C4">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1443,10 +1440,10 @@
         <v>42</v>
       </c>
       <c r="B5">
-        <v>60.8</v>
+        <v>61.7</v>
       </c>
       <c r="C5">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1454,10 +1451,10 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>87.2</v>
+        <v>88.7</v>
       </c>
       <c r="C6">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1465,10 +1462,10 @@
         <v>44</v>
       </c>
       <c r="B7">
-        <v>90.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="C7">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1476,10 +1473,10 @@
         <v>45</v>
       </c>
       <c r="B8">
-        <v>94.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C8">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1487,10 +1484,10 @@
         <v>46</v>
       </c>
       <c r="B9">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C9">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1498,10 +1495,10 @@
         <v>47</v>
       </c>
       <c r="B10">
-        <v>98.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C10">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1509,10 +1506,10 @@
         <v>48</v>
       </c>
       <c r="B11">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C11">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1520,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="B12">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1534,7 +1531,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1545,7 +1542,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1556,18 +1553,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
-      <c r="C16">
-        <v>1361</v>
+        <v>1424</v>
       </c>
     </row>
   </sheetData>
@@ -1582,79 +1568,79 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="C2">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C3">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C4">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C5">
-        <v>11.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C6">
-        <v>10.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1662,10 +1648,10 @@
         <v>39</v>
       </c>
       <c r="B8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1676,15 +1662,15 @@
         <v>27</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>0.8</v>
@@ -1692,7 +1678,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1713,13 +1699,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -1727,24 +1713,24 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>3</v>
-      </c>
-      <c r="D2">
-        <v>2.3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1755,10 +1741,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1769,21 +1755,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>21</v>
@@ -1797,7 +1783,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>35</v>
@@ -1811,52 +1797,52 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1867,16 +1853,16 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="C12">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D12">
-        <v>15.8</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1891,7 +1877,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1905,63 +1891,63 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>44.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C3">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>19.9</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>21</v>
@@ -1975,7 +1961,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>35</v>
@@ -1989,72 +1975,72 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>34.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>24.3</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="C12">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D12">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
     </row>
   </sheetData>
@@ -2069,46 +2055,46 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>788</v>
+        <v>822</v>
       </c>
       <c r="C2">
-        <v>98.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2123,46 +2109,46 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3">
-        <v>984</v>
+        <v>1031</v>
       </c>
       <c r="C3">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C4">
-        <v>25.7</v>
+        <v>26.2</v>
       </c>
     </row>
   </sheetData>
@@ -2177,18 +2163,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -2199,24 +2185,24 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4">
-        <v>815</v>
+        <v>854</v>
       </c>
       <c r="C4">
-        <v>59.9</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
